--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_90_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_90_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>7</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2119,10 +2119,10 @@
         <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>2</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>112</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -4292,10 +4292,10 @@
         <v>17</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>2</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>87</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
         <v>23</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_90_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_90_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -695,17 +695,17 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
         <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>65.71</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" t="n">
-        <v>8</v>
-      </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
         <v>7</v>
       </c>
-      <c r="Y19" t="n">
-        <v>10</v>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3354,11 +3354,11 @@
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
         <v>3</v>
       </c>
-      <c r="Y28" t="n">
-        <v>5</v>
-      </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6796,14 +6796,14 @@
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
